--- a/Inserter/InsertForm.xlsx
+++ b/Inserter/InsertForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\some folder\indDictionary\Dictionary-SQLite\Inserter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42C11D0-15C3-4C31-B9DD-7BD4FF2175C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FE8543-947A-497F-9166-04BC74B18573}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{F8C86FE8-8F11-4F2F-A93D-043197A8D0DA}"/>
+    <workbookView xWindow="2325" yWindow="1500" windowWidth="21600" windowHeight="11385" xr2:uid="{E3F2CDA7-9D83-48EB-84BB-07F72F5D0A76}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="788">
   <si>
     <t>слово</t>
   </si>
@@ -45,28 +45,2356 @@
     <t>дата</t>
   </si>
   <si>
-    <t>qqq</t>
-  </si>
-  <si>
-    <t>aaa</t>
-  </si>
-  <si>
-    <t>first</t>
-  </si>
-  <si>
-    <t>ffff</t>
-  </si>
-  <si>
-    <t>fww</t>
-  </si>
-  <si>
-    <t>fwfwe</t>
-  </si>
-  <si>
-    <t>dfwf</t>
-  </si>
-  <si>
-    <t>second</t>
+    <t xml:space="preserve"> (грецкий) орех</t>
+  </si>
+  <si>
+    <t>орах (orah)</t>
+  </si>
+  <si>
+    <t>500 слов</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> август</t>
+  </si>
+  <si>
+    <t>август (avgust)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> адрес</t>
+  </si>
+  <si>
+    <t>адреса (adresa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> апельсин</t>
+  </si>
+  <si>
+    <t>наранџаст (narandžast)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> апрель</t>
+  </si>
+  <si>
+    <t>април (april)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> аутобус</t>
+  </si>
+  <si>
+    <t>аутобус (autobus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> бабушка</t>
+  </si>
+  <si>
+    <t>бака (baka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> балкон</t>
+  </si>
+  <si>
+    <t>балкон (balkon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> банан</t>
+  </si>
+  <si>
+    <t>банана (banana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> бедный</t>
+  </si>
+  <si>
+    <t>сиромашан [siromašan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> без</t>
+  </si>
+  <si>
+    <t>без (bez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> белый</t>
+  </si>
+  <si>
+    <t>бео (beo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> близко (от), рядом</t>
+  </si>
+  <si>
+    <t>близу (blizu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> блузка</t>
+  </si>
+  <si>
+    <t>блуза (bluza)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> богатый</t>
+  </si>
+  <si>
+    <t>богат [bogat]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> больница</t>
+  </si>
+  <si>
+    <t>болница (bolnica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> больной</t>
+  </si>
+  <si>
+    <t>болестан [bolestan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> большой</t>
+  </si>
+  <si>
+    <t>велик [velik]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> брат</t>
+  </si>
+  <si>
+    <t>брат (brat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> брюки</t>
+  </si>
+  <si>
+    <t>панталоне (pantalone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> булочка</t>
+  </si>
+  <si>
+    <t>земичка (zemička)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> бумага</t>
+  </si>
+  <si>
+    <t>папир (papir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> бутылка</t>
+  </si>
+  <si>
+    <t>боца (boca)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> быть должным</t>
+  </si>
+  <si>
+    <t>морати [morati]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> в</t>
+  </si>
+  <si>
+    <t>у (u)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ванная</t>
+  </si>
+  <si>
+    <t>купатило (kupatilo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> варенье</t>
+  </si>
+  <si>
+    <t>пекмез (pekmez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ваш</t>
+  </si>
+  <si>
+    <t>ваш (vaš)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> велосипед</t>
+  </si>
+  <si>
+    <t>бицикл (bicikl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> весна</t>
+  </si>
+  <si>
+    <t>пролеће (proleće)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ветер</t>
+  </si>
+  <si>
+    <t>ветар (vetar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вечер</t>
+  </si>
+  <si>
+    <t>вечер (večer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вечеринка</t>
+  </si>
+  <si>
+    <t>журка (žurka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вещь</t>
+  </si>
+  <si>
+    <t>ствар (stvar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вилка</t>
+  </si>
+  <si>
+    <t>виљушка (viljuška)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> виноград</t>
+  </si>
+  <si>
+    <t>грожђе (grožđe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вместе</t>
+  </si>
+  <si>
+    <t>заjедно [zajedno]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вода</t>
+  </si>
+  <si>
+    <t>вода (voda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> водитель</t>
+  </si>
+  <si>
+    <t>возач (vozač)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> возле</t>
+  </si>
+  <si>
+    <t>поред (pored)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вон тот</t>
+  </si>
+  <si>
+    <t>oнаj [onaj]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вопрос</t>
+  </si>
+  <si>
+    <t>питање (pitanje)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> восемнадцать</t>
+  </si>
+  <si>
+    <t>осамнаест (osamnaest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> восемь</t>
+  </si>
+  <si>
+    <t>осам (osam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> восемьдесят</t>
+  </si>
+  <si>
+    <t>осамдесет (osamdeset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> воскресенье; неделя</t>
+  </si>
+  <si>
+    <t>недеља (nedelja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> врач</t>
+  </si>
+  <si>
+    <t>лекар (lekar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> время, погода</t>
+  </si>
+  <si>
+    <t>време (vreme)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вторник</t>
+  </si>
+  <si>
+    <t>уторак (utorak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вчера</t>
+  </si>
+  <si>
+    <t>јуче (juče)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вы</t>
+  </si>
+  <si>
+    <t>ви (vi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> высокий</t>
+  </si>
+  <si>
+    <t>висок [visok]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> газировка</t>
+  </si>
+  <si>
+    <t>газирани сок (gazirani sok)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> галстук</t>
+  </si>
+  <si>
+    <t>кравата (kravata)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> где</t>
+  </si>
+  <si>
+    <t>где (gde)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> глупый</t>
+  </si>
+  <si>
+    <t>глуп [glup]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> год</t>
+  </si>
+  <si>
+    <t>година (godina)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> голодный</t>
+  </si>
+  <si>
+    <t>гладан [gladan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> голубой</t>
+  </si>
+  <si>
+    <t>плав (plav)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> гора</t>
+  </si>
+  <si>
+    <t>планина (planina)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> город</t>
+  </si>
+  <si>
+    <t>град (grad)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> горячий</t>
+  </si>
+  <si>
+    <t>врућ [vruć]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> гостиница</t>
+  </si>
+  <si>
+    <t>хотел (hotel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> гость</t>
+  </si>
+  <si>
+    <t>гост (gost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> готовый</t>
+  </si>
+  <si>
+    <t>спреман [spreman]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> гриб</t>
+  </si>
+  <si>
+    <t>гљива (gljiva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> два</t>
+  </si>
+  <si>
+    <t>два (dva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> двадцать</t>
+  </si>
+  <si>
+    <t>двадесет (dvadeset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> двенадцать</t>
+  </si>
+  <si>
+    <t>дванаест (dvanaest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дверь</t>
+  </si>
+  <si>
+    <t>врата (vrata)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> девочка</t>
+  </si>
+  <si>
+    <t>девоjчица (devojčica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> девяносто</t>
+  </si>
+  <si>
+    <t>деведесет (devedeset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> девятнадцать</t>
+  </si>
+  <si>
+    <t>деветнаест (devetnaest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> девять</t>
+  </si>
+  <si>
+    <t>девет (devet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дед</t>
+  </si>
+  <si>
+    <t>деда (deda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> декабрь</t>
+  </si>
+  <si>
+    <t>децембар (decembar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> день</t>
+  </si>
+  <si>
+    <t>дан (dan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> день рождения</t>
+  </si>
+  <si>
+    <t>рођендан (rodžendan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> деньги</t>
+  </si>
+  <si>
+    <t>новац (novac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дерево</t>
+  </si>
+  <si>
+    <t>дрво (drvo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> десять</t>
+  </si>
+  <si>
+    <t>десет (deset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дешёвый</t>
+  </si>
+  <si>
+    <t>jефтин [jeftin]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> диван</t>
+  </si>
+  <si>
+    <t>софа (sofa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> для; через (о времени)</t>
+  </si>
+  <si>
+    <t>за (za)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> до</t>
+  </si>
+  <si>
+    <t>до (do)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> до свидания</t>
+  </si>
+  <si>
+    <t>довиђења (doviđenja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> добро пожаловать</t>
+  </si>
+  <si>
+    <t>добродошли (dobrodošli)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дождь</t>
+  </si>
+  <si>
+    <t>киша (kiša)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> долгий, длинный</t>
+  </si>
+  <si>
+    <t>дуг [dug]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дом</t>
+  </si>
+  <si>
+    <t>кућа (kuća)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дорога</t>
+  </si>
+  <si>
+    <t>пут (пут)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дорогой</t>
+  </si>
+  <si>
+    <t>скуп [skup]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> дочь</t>
+  </si>
+  <si>
+    <t>ћерка (ćerka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> друг</t>
+  </si>
+  <si>
+    <t>пријатељ (prijatelj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> душ</t>
+  </si>
+  <si>
+    <t>туш (tuš)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> его</t>
+  </si>
+  <si>
+    <t>његов (njegov)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> еда</t>
+  </si>
+  <si>
+    <t>храна (hrana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> если</t>
+  </si>
+  <si>
+    <t>ако [ako]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> её</t>
+  </si>
+  <si>
+    <t>њен (njen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> женатый</t>
+  </si>
+  <si>
+    <t>ожењен (oženjen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> женщина, жена</t>
+  </si>
+  <si>
+    <t>жена (žena)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> животное</t>
+  </si>
+  <si>
+    <t>животиња (životinja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> жить</t>
+  </si>
+  <si>
+    <t>живети [živjeti]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> жёлтый</t>
+  </si>
+  <si>
+    <t>жут (žut)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> завод</t>
+  </si>
+  <si>
+    <t>фабрика (fabrika)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> завтра</t>
+  </si>
+  <si>
+    <t>сутра (sutra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> завтрак</t>
+  </si>
+  <si>
+    <t>доручак (doručak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> зал, гостиная</t>
+  </si>
+  <si>
+    <t>дневна соба (dnevna soba)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> замужняя</t>
+  </si>
+  <si>
+    <t>удата (udata)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> занятый</t>
+  </si>
+  <si>
+    <t>заузет [zauzet]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> здание</t>
+  </si>
+  <si>
+    <t>зграда (zgrada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> здоровый</t>
+  </si>
+  <si>
+    <t>здрав [zdrav]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> зеленый</t>
+  </si>
+  <si>
+    <t>зелен (zelen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> зеркало</t>
+  </si>
+  <si>
+    <t>огледало (ogledalo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> зима</t>
+  </si>
+  <si>
+    <t>зима (zima)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> игрушка</t>
+  </si>
+  <si>
+    <t>играчка (igračka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> из (о материале)</t>
+  </si>
+  <si>
+    <t>од (od)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> из (откуда</t>
+  </si>
+  <si>
+    <t>из (iz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> извини</t>
+  </si>
+  <si>
+    <t>извини (izvini)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> имя</t>
+  </si>
+  <si>
+    <t>име (ime)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> инженер</t>
+  </si>
+  <si>
+    <t>инжењер (inženjer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> их</t>
+  </si>
+  <si>
+    <t>њихов (njihov)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> июль</t>
+  </si>
+  <si>
+    <t>jули (јuli)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> июнь</t>
+  </si>
+  <si>
+    <t>jун (jun)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> как</t>
+  </si>
+  <si>
+    <t>како (kako)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> капуста</t>
+  </si>
+  <si>
+    <t>купус (kupus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> карандаш</t>
+  </si>
+  <si>
+    <t>оловка (olovka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> карта, карточка, билет</t>
+  </si>
+  <si>
+    <t>карта (karta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> картина, фотография</t>
+  </si>
+  <si>
+    <t>слика (slika)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> картофель</t>
+  </si>
+  <si>
+    <t>кромпир (krompir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> каша</t>
+  </si>
+  <si>
+    <t>каша (kaša)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> квартира</t>
+  </si>
+  <si>
+    <t>стан (stan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кинотеатр</t>
+  </si>
+  <si>
+    <t>биоскоп (bioskop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ключ</t>
+  </si>
+  <si>
+    <t>кључ (ključ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> книга</t>
+  </si>
+  <si>
+    <t>књига (knjiga)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ковер</t>
+  </si>
+  <si>
+    <t>тепих (tepih)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> когда</t>
+  </si>
+  <si>
+    <t>када (kada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> колбаса</t>
+  </si>
+  <si>
+    <t>кобасица (kobasica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> комната</t>
+  </si>
+  <si>
+    <t>соба (soba)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> компьютер</t>
+  </si>
+  <si>
+    <t>рачунар (računar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> конфета</t>
+  </si>
+  <si>
+    <t>бомбона (bombona)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> корабль</t>
+  </si>
+  <si>
+    <t>брод (brod)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> коридор</t>
+  </si>
+  <si>
+    <t>ходник (hodnik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> коричневый</t>
+  </si>
+  <si>
+    <t>браон (braon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> коробка</t>
+  </si>
+  <si>
+    <t>кутија (kutija)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> короткий</t>
+  </si>
+  <si>
+    <t>кратак [kratak]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> костюм</t>
+  </si>
+  <si>
+    <t>одело (odelo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кофе</t>
+  </si>
+  <si>
+    <t>кафа (kafa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кошка</t>
+  </si>
+  <si>
+    <t>мачка (mačka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> красивый, хороший</t>
+  </si>
+  <si>
+    <t>леп [lep]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> красный</t>
+  </si>
+  <si>
+    <t>црвен (crven)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кресло</t>
+  </si>
+  <si>
+    <t>фотеља (fotelja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кровать</t>
+  </si>
+  <si>
+    <t>кревет (krevet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кто</t>
+  </si>
+  <si>
+    <t>ко (ko)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> куда</t>
+  </si>
+  <si>
+    <t>куда (kuda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кукуруза</t>
+  </si>
+  <si>
+    <t>кукуруз (kukuruz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> курица, цыпленок</t>
+  </si>
+  <si>
+    <t>пиле (pile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> куртка</t>
+  </si>
+  <si>
+    <t>јакна (jakna)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кухня</t>
+  </si>
+  <si>
+    <t>кухиња (kuhinja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> лампа</t>
+  </si>
+  <si>
+    <t>лампа (lampa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> легкий</t>
+  </si>
+  <si>
+    <t>лак [lak]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> лето</t>
+  </si>
+  <si>
+    <t>лето (leto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> лимон</t>
+  </si>
+  <si>
+    <t>лимун (limun)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> линейка</t>
+  </si>
+  <si>
+    <t>лењир (lenjir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ложка</t>
+  </si>
+  <si>
+    <t>кашика (kašika)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> лук</t>
+  </si>
+  <si>
+    <t>лук (luk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> люди</t>
+  </si>
+  <si>
+    <t>људи (ljudi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> магазин</t>
+  </si>
+  <si>
+    <t>продавница (prodavnica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> май</t>
+  </si>
+  <si>
+    <t>мај (maj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> маленький</t>
+  </si>
+  <si>
+    <t>мал [mal]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мальчик</t>
+  </si>
+  <si>
+    <t>дечак (dečak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> март</t>
+  </si>
+  <si>
+    <t>март (mart)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> масло сливочное</t>
+  </si>
+  <si>
+    <t>маслац (maslac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мать</t>
+  </si>
+  <si>
+    <t>мајка (majka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> машина</t>
+  </si>
+  <si>
+    <t>кола (kola)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мебель</t>
+  </si>
+  <si>
+    <t>намештај (nameštaj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> медсестра</t>
+  </si>
+  <si>
+    <t>медицинска сестра (medicinska sestra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> месец</t>
+  </si>
+  <si>
+    <t>месец (mesec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> место</t>
+  </si>
+  <si>
+    <t>место (mesto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> минута</t>
+  </si>
+  <si>
+    <t>минута (minuta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мой</t>
+  </si>
+  <si>
+    <t>мој (moj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> молодой</t>
+  </si>
+  <si>
+    <t>млад [mlad]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> молоко</t>
+  </si>
+  <si>
+    <t>млеко (mleko)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> морковь</t>
+  </si>
+  <si>
+    <t>шаргарепа (šargarepa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мороженое</t>
+  </si>
+  <si>
+    <t>сладолед (sladoled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> муж</t>
+  </si>
+  <si>
+    <t>муж (muž)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мужчина</t>
+  </si>
+  <si>
+    <t>мушкарац (muškarac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> музыка</t>
+  </si>
+  <si>
+    <t>музика (muzika)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мы</t>
+  </si>
+  <si>
+    <t>ми (mi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мыло</t>
+  </si>
+  <si>
+    <t>сапун (sapun)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мясо</t>
+  </si>
+  <si>
+    <t>месо (meso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мяч</t>
+  </si>
+  <si>
+    <t>лопта (lopta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мёд</t>
+  </si>
+  <si>
+    <t>мед (med)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> на</t>
+  </si>
+  <si>
+    <t>на (na)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> над</t>
+  </si>
+  <si>
+    <t>изнад (iznad)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> наш</t>
+  </si>
+  <si>
+    <t>наш (naš)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> небо</t>
+  </si>
+  <si>
+    <t>небо (nebo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> несколько</t>
+  </si>
+  <si>
+    <t>неколико [nekoliko]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> низкий</t>
+  </si>
+  <si>
+    <t>низак [nizak]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> никогда</t>
+  </si>
+  <si>
+    <t>никад [nikad]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> новый</t>
+  </si>
+  <si>
+    <t>нов [nov]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> нож</t>
+  </si>
+  <si>
+    <t>нож (nož)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ноль</t>
+  </si>
+  <si>
+    <t>нула (nula)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> носок</t>
+  </si>
+  <si>
+    <t>чарапа (čarapa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ночь</t>
+  </si>
+  <si>
+    <t>ноћ (noć)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ноябрь</t>
+  </si>
+  <si>
+    <t>новембар (novembar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> о</t>
+  </si>
+  <si>
+    <t>о (o)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> обед</t>
+  </si>
+  <si>
+    <t>ручак (ručak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> обычно</t>
+  </si>
+  <si>
+    <t>обично [obično]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> овощи</t>
+  </si>
+  <si>
+    <t>поврће (povrće)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> огурец</t>
+  </si>
+  <si>
+    <t>краставац (krastavac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> одежда</t>
+  </si>
+  <si>
+    <t>одећа (odeća)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> один</t>
+  </si>
+  <si>
+    <t>један(jedan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> одиннадцать</t>
+  </si>
+  <si>
+    <t>једанаест (jedanaest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> окно</t>
+  </si>
+  <si>
+    <t>прозор (prozor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> октябрь</t>
+  </si>
+  <si>
+    <t>oктобар (oktobar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> он</t>
+  </si>
+  <si>
+    <t>он (on)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> она</t>
+  </si>
+  <si>
+    <t>oна (ona)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> они</t>
+  </si>
+  <si>
+    <t>oni (oni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> оно</t>
+  </si>
+  <si>
+    <t>оно (ono)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> осень</t>
+  </si>
+  <si>
+    <t>јесен (jesen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> отвечать</t>
+  </si>
+  <si>
+    <t>одговарати [odgovarati]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> отец</t>
+  </si>
+  <si>
+    <t>отац (otac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> официант</t>
+  </si>
+  <si>
+    <t>конобар (konobar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> очки</t>
+  </si>
+  <si>
+    <t>наочаре (naočare)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> пальто</t>
+  </si>
+  <si>
+    <t>капут (kaput)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> перед (в пространстве)</t>
+  </si>
+  <si>
+    <t>испред (ispred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> перед (во времени)</t>
+  </si>
+  <si>
+    <t>пре (pre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> перец</t>
+  </si>
+  <si>
+    <t>бибер (biber)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> перчатки</t>
+  </si>
+  <si>
+    <t>рукавице (rukavice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> песня</t>
+  </si>
+  <si>
+    <t>песма (pesma)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> петь</t>
+  </si>
+  <si>
+    <t>певати [pevati]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> печальный</t>
+  </si>
+  <si>
+    <t>tužan [тужан]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> печенье</t>
+  </si>
+  <si>
+    <t>колачић (kolačić)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> пирог</t>
+  </si>
+  <si>
+    <t>пита (pita)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> письмо</t>
+  </si>
+  <si>
+    <t>писмо (pismo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> платье</t>
+  </si>
+  <si>
+    <t>хаљина (haljina)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> плохой</t>
+  </si>
+  <si>
+    <t>лош [loš]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> площадь</t>
+  </si>
+  <si>
+    <t>trg (trg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> под</t>
+  </si>
+  <si>
+    <t>испод (ispod)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> подарок</t>
+  </si>
+  <si>
+    <t>поклон (poklon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> поезд</t>
+  </si>
+  <si>
+    <t>воз (voz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> пожалуйста</t>
+  </si>
+  <si>
+    <t>молим (molim)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> поздний</t>
+  </si>
+  <si>
+    <t>касан [kasan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> пол</t>
+  </si>
+  <si>
+    <t>под (pod)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> полка</t>
+  </si>
+  <si>
+    <t>полица (polica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> полотенце</t>
+  </si>
+  <si>
+    <t>пешкир (peškir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> помагать</t>
+  </si>
+  <si>
+    <t>помагати [pomagati]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> помидор</t>
+  </si>
+  <si>
+    <t>парадаjз (paradajz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> понедельник</t>
+  </si>
+  <si>
+    <t>понедељак (ponedeljak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> потом</t>
+  </si>
+  <si>
+    <t>онда [onda]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> почему</t>
+  </si>
+  <si>
+    <t>зашто (zašto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> почта</t>
+  </si>
+  <si>
+    <t>пошта (pošta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> праздник</t>
+  </si>
+  <si>
+    <t>празник (praznik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> проблема</t>
+  </si>
+  <si>
+    <t>проблем (problem)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> продавец</t>
+  </si>
+  <si>
+    <t>продавац (prodavac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> прошлый</t>
+  </si>
+  <si>
+    <t>прошли [prošli]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> прыгать</t>
+  </si>
+  <si>
+    <t>скакати [skakati]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> птица</t>
+  </si>
+  <si>
+    <t>птица (ptica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> пятнадцать</t>
+  </si>
+  <si>
+    <t>петнаест (petnaest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> пятница</t>
+  </si>
+  <si>
+    <t>петак (petak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> пять</t>
+  </si>
+  <si>
+    <t>пет (pet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> пятьдесят</t>
+  </si>
+  <si>
+    <t>педесет (pedeset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> работа</t>
+  </si>
+  <si>
+    <t>посао (posao)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> рабочий</t>
+  </si>
+  <si>
+    <t>радник (radnik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> радостный</t>
+  </si>
+  <si>
+    <t>радостан [radostan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ранний</t>
+  </si>
+  <si>
+    <t>рани [rani]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> расческа</t>
+  </si>
+  <si>
+    <t>чешаљ (češalj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ребенок</t>
+  </si>
+  <si>
+    <t>дете (dete)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> река</t>
+  </si>
+  <si>
+    <t>река (reka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ресторан</t>
+  </si>
+  <si>
+    <t>ресторан (restoran)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> рис</t>
+  </si>
+  <si>
+    <t>пиринач (pirinač)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> родители</t>
+  </si>
+  <si>
+    <t>родитељи (roditelji)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> розовый</t>
+  </si>
+  <si>
+    <t>розе (roze)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> рубашка</t>
+  </si>
+  <si>
+    <t>кошуља (košulja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ручка</t>
+  </si>
+  <si>
+    <t>перо (pero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> рыба</t>
+  </si>
+  <si>
+    <t>риба (riba)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> с</t>
+  </si>
+  <si>
+    <t>с(a) (s(a))</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сад</t>
+  </si>
+  <si>
+    <t>врт (vrt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> салат</t>
+  </si>
+  <si>
+    <t>салата (salata)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> салфетка</t>
+  </si>
+  <si>
+    <t>салвета (salveta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> самолет</t>
+  </si>
+  <si>
+    <t>авион (avion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сахар</t>
+  </si>
+  <si>
+    <t>шећер (šećer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> светлый</t>
+  </si>
+  <si>
+    <t>светао [svetao]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> свитер</t>
+  </si>
+  <si>
+    <t>џемпер (džemper)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> свободный</t>
+  </si>
+  <si>
+    <t>слободан [slobodan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сегодня</t>
+  </si>
+  <si>
+    <t>данас (danas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> семнадцать</t>
+  </si>
+  <si>
+    <t>седамнаест (sedamnaest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> семь</t>
+  </si>
+  <si>
+    <t>седам (sedam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> семьдесят</t>
+  </si>
+  <si>
+    <t>седамдесет (sedamdeset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> семья</t>
+  </si>
+  <si>
+    <t>породица (porodica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сендвич, бутерброд</t>
+  </si>
+  <si>
+    <t>сендвич (sendvič)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сентябрь</t>
+  </si>
+  <si>
+    <t>септембар (septembar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> серый</t>
+  </si>
+  <si>
+    <t>сив (siv)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сестра</t>
+  </si>
+  <si>
+    <t>сестра (sestra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> синий</t>
+  </si>
+  <si>
+    <t>модар (modar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сколько</t>
+  </si>
+  <si>
+    <t>колико (koliko)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> следующий</t>
+  </si>
+  <si>
+    <t>следећи [sledeći]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> снег</t>
+  </si>
+  <si>
+    <t>снег (sneg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> собака</t>
+  </si>
+  <si>
+    <t>пас (pas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сок</t>
+  </si>
+  <si>
+    <t>сок (sok)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> солнце</t>
+  </si>
+  <si>
+    <t>сунце (sunce)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> соль</t>
+  </si>
+  <si>
+    <t>со (so)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сорок</t>
+  </si>
+  <si>
+    <t>четрдесет (četrdeset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> спальня</t>
+  </si>
+  <si>
+    <t>спаваћа соба (spavaća soba)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> спасибо</t>
+  </si>
+  <si>
+    <t>хвала (hvala)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> спать</t>
+  </si>
+  <si>
+    <t>спавати [spavati]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> среда</t>
+  </si>
+  <si>
+    <t>среда (sreda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> стакан</t>
+  </si>
+  <si>
+    <t>чаша (čaša)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> станция, остановка</t>
+  </si>
+  <si>
+    <t>станица (stanica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> старый</t>
+  </si>
+  <si>
+    <t>стар [star]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> стена</t>
+  </si>
+  <si>
+    <t>зид (zid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сто</t>
+  </si>
+  <si>
+    <t>сто (sto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> стол</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> страна, земля</t>
+  </si>
+  <si>
+    <t>земља (zemlja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> студент</t>
+  </si>
+  <si>
+    <t>студент (student)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> стул</t>
+  </si>
+  <si>
+    <t>столица (stolica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> суббота</t>
+  </si>
+  <si>
+    <t>субота (subota)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сумка</t>
+  </si>
+  <si>
+    <t>торба (torba)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> суп</t>
+  </si>
+  <si>
+    <t>супа (supa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> счастье</t>
+  </si>
+  <si>
+    <t>срећа (sreća)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> счет</t>
+  </si>
+  <si>
+    <t>рачун (račun)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сын</t>
+  </si>
+  <si>
+    <t>син (sin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сыр</t>
+  </si>
+  <si>
+    <t>сир (sir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> танцевать</t>
+  </si>
+  <si>
+    <t>плесати [plesati]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> тарелка; блюдце</t>
+  </si>
+  <si>
+    <t>тањир (tanjir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> твой</t>
+  </si>
+  <si>
+    <t>твоj (tvoj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> театр</t>
+  </si>
+  <si>
+    <t>позориште (pozorište)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> телевизор</t>
+  </si>
+  <si>
+    <t>телевизор (televizor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> телефон</t>
+  </si>
+  <si>
+    <t>телефон (telefon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> темный</t>
+  </si>
+  <si>
+    <t>таман [taman]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> тетрадь</t>
+  </si>
+  <si>
+    <t>свеска (sveska)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> тоже</t>
+  </si>
+  <si>
+    <t>такође [takođe]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> торт</t>
+  </si>
+  <si>
+    <t>торта (torta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> трамвай</t>
+  </si>
+  <si>
+    <t>трамвај (tramvaj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> три</t>
+  </si>
+  <si>
+    <t>три (tri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> тридцать</t>
+  </si>
+  <si>
+    <t>тридесет (trideset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> тринадцать</t>
+  </si>
+  <si>
+    <t>тринаест (тринаест)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> туфли</t>
+  </si>
+  <si>
+    <t>ципеле (cipele)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ты</t>
+  </si>
+  <si>
+    <t>ти (ti)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> тысяча</t>
+  </si>
+  <si>
+    <t>хиљада (hiljada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> тяжелый, трудный</t>
+  </si>
+  <si>
+    <t>тежак [težak]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> тёплый</t>
+  </si>
+  <si>
+    <t>topao [topao]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ужин</t>
+  </si>
+  <si>
+    <t>вечера (večera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> улица</t>
+  </si>
+  <si>
+    <t>улица (ulica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> умный</t>
+  </si>
+  <si>
+    <t>паметан [pametan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> утро</t>
+  </si>
+  <si>
+    <t>јутро (jutro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> утюг</t>
+  </si>
+  <si>
+    <t>пегла (pegla)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> учитель</t>
+  </si>
+  <si>
+    <t>учитељ (učitelj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> фамилия</t>
+  </si>
+  <si>
+    <t>презиме (prezime)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> февраль</t>
+  </si>
+  <si>
+    <t>фебруар (februar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> фрукты</t>
+  </si>
+  <si>
+    <t>воће (voće)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> футболка</t>
+  </si>
+  <si>
+    <t>мајица (majica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> хлеб</t>
+  </si>
+  <si>
+    <t>хлеб (hleb)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> холодильник</t>
+  </si>
+  <si>
+    <t>фрижидер (frižider)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> холодный</t>
+  </si>
+  <si>
+    <t>хладан [hladan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> хороший</t>
+  </si>
+  <si>
+    <t>добар [dobar]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> цвет</t>
+  </si>
+  <si>
+    <t>боја (boja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> цветок</t>
+  </si>
+  <si>
+    <t>цвет (cvet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> центр</t>
+  </si>
+  <si>
+    <t>центар (centar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> церковь</t>
+  </si>
+  <si>
+    <t>црква (crkva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> чай</t>
+  </si>
+  <si>
+    <t>чаj (čaj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> час; часы</t>
+  </si>
+  <si>
+    <t>сат (sat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> чашка</t>
+  </si>
+  <si>
+    <t>шоља (šolja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> человек</t>
+  </si>
+  <si>
+    <t>човек (čovek)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> через (отверстие)</t>
+  </si>
+  <si>
+    <t>кроз (kroz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> через (поле)</t>
+  </si>
+  <si>
+    <t>преко (preko)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> черный</t>
+  </si>
+  <si>
+    <t>црн (crn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> четверг</t>
+  </si>
+  <si>
+    <t>четвртак (četvrtak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> четыре</t>
+  </si>
+  <si>
+    <t>четири (četiri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> четырнадцать</t>
+  </si>
+  <si>
+    <t>четрнаест (četrnaest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> число, номер</t>
+  </si>
+  <si>
+    <t>број (broj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> что</t>
+  </si>
+  <si>
+    <t>шта (šta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шапка, кепка</t>
+  </si>
+  <si>
+    <t>капа (kapa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шарф</t>
+  </si>
+  <si>
+    <t>шал (šal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шестнадцать</t>
+  </si>
+  <si>
+    <t>шеснаест (šesnaest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шесть</t>
+  </si>
+  <si>
+    <t>шест (šest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шестьдесят</t>
+  </si>
+  <si>
+    <t>шездесет (šezdeset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шкаф</t>
+  </si>
+  <si>
+    <t>орман (orman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> школа</t>
+  </si>
+  <si>
+    <t>школа (škola)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шляпа</t>
+  </si>
+  <si>
+    <t>шешир (šešir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шоколад</t>
+  </si>
+  <si>
+    <t>чоколада (čokolada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шорты</t>
+  </si>
+  <si>
+    <t>шорц (šorc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> шутить</t>
+  </si>
+  <si>
+    <t>шалити се [šaliti se]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> этаж</t>
+  </si>
+  <si>
+    <t>спрат (sprat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> этот</t>
+  </si>
+  <si>
+    <t>оваj [ovaj]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> юбка</t>
+  </si>
+  <si>
+    <t>сукња (suknja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> я</t>
+  </si>
+  <si>
+    <t>jа (ja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> яблоко</t>
+  </si>
+  <si>
+    <t>jabuka (jabuka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ягода</t>
+  </si>
+  <si>
+    <t>бобица (bobica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> яйцо</t>
+  </si>
+  <si>
+    <t>јаје (jаје)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> январь</t>
+  </si>
+  <si>
+    <t>jануар (januar)</t>
   </si>
 </sst>
 </file>
@@ -103,8 +2431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -419,8 +2746,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2FAF173-5C89-462F-9740-7582F3744311}">
-  <dimension ref="B1:E4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C3E5FD-FB59-45AE-BE60-9EDE9847AC6E}">
+  <dimension ref="B1:E393"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="30.7109375" customWidth="1"/>
@@ -443,36 +2770,4315 @@
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56" t="s">
+        <v>114</v>
+      </c>
+      <c r="D56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62" t="s">
+        <v>126</v>
+      </c>
+      <c r="D62" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D65" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>133</v>
+      </c>
+      <c r="C66" t="s">
+        <v>134</v>
+      </c>
+      <c r="D66" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>135</v>
+      </c>
+      <c r="C67" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>137</v>
+      </c>
+      <c r="C68" t="s">
+        <v>138</v>
+      </c>
+      <c r="D68" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69" t="s">
+        <v>140</v>
+      </c>
+      <c r="D69" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" t="s">
+        <v>142</v>
+      </c>
+      <c r="D70" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72" t="s">
+        <v>146</v>
+      </c>
+      <c r="D72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" t="s">
+        <v>148</v>
+      </c>
+      <c r="D73" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" t="s">
+        <v>150</v>
+      </c>
+      <c r="D74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" t="s">
+        <v>152</v>
+      </c>
+      <c r="D75" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" t="s">
+        <v>154</v>
+      </c>
+      <c r="D76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" t="s">
+        <v>156</v>
+      </c>
+      <c r="D77" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>157</v>
+      </c>
+      <c r="C78" t="s">
+        <v>158</v>
+      </c>
+      <c r="D78" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>159</v>
+      </c>
+      <c r="C79" t="s">
+        <v>160</v>
+      </c>
+      <c r="D79" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>161</v>
+      </c>
+      <c r="C80" t="s">
+        <v>162</v>
+      </c>
+      <c r="D80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>163</v>
+      </c>
+      <c r="C81" t="s">
+        <v>164</v>
+      </c>
+      <c r="D81" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>165</v>
+      </c>
+      <c r="C82" t="s">
+        <v>166</v>
+      </c>
+      <c r="D82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" t="s">
+        <v>168</v>
+      </c>
+      <c r="D83" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>169</v>
+      </c>
+      <c r="C84" t="s">
+        <v>170</v>
+      </c>
+      <c r="D84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" t="s">
+        <v>172</v>
+      </c>
+      <c r="D85" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86" t="s">
+        <v>174</v>
+      </c>
+      <c r="D86" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>175</v>
+      </c>
+      <c r="C87" t="s">
+        <v>176</v>
+      </c>
+      <c r="D87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>177</v>
+      </c>
+      <c r="C88" t="s">
+        <v>178</v>
+      </c>
+      <c r="D88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>179</v>
+      </c>
+      <c r="C89" t="s">
+        <v>180</v>
+      </c>
+      <c r="D89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90" t="s">
+        <v>182</v>
+      </c>
+      <c r="D90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91" t="s">
+        <v>184</v>
+      </c>
+      <c r="D91" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92" t="s">
+        <v>186</v>
+      </c>
+      <c r="D92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" t="s">
+        <v>188</v>
+      </c>
+      <c r="D93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94" t="s">
+        <v>190</v>
+      </c>
+      <c r="D94" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>191</v>
+      </c>
+      <c r="C95" t="s">
+        <v>192</v>
+      </c>
+      <c r="D95" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" t="s">
+        <v>194</v>
+      </c>
+      <c r="D96" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>195</v>
+      </c>
+      <c r="C97" t="s">
+        <v>196</v>
+      </c>
+      <c r="D97" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>197</v>
+      </c>
+      <c r="C98" t="s">
+        <v>198</v>
+      </c>
+      <c r="D98" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>199</v>
+      </c>
+      <c r="C99" t="s">
+        <v>200</v>
+      </c>
+      <c r="D99" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>201</v>
+      </c>
+      <c r="C100" t="s">
+        <v>202</v>
+      </c>
+      <c r="D100" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>203</v>
+      </c>
+      <c r="C101" t="s">
+        <v>204</v>
+      </c>
+      <c r="D101" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>205</v>
+      </c>
+      <c r="C102" t="s">
+        <v>206</v>
+      </c>
+      <c r="D102" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>207</v>
+      </c>
+      <c r="C103" t="s">
+        <v>208</v>
+      </c>
+      <c r="D103" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>209</v>
+      </c>
+      <c r="C104" t="s">
+        <v>210</v>
+      </c>
+      <c r="D104" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" t="s">
+        <v>212</v>
+      </c>
+      <c r="D105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" t="s">
+        <v>214</v>
+      </c>
+      <c r="D106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>215</v>
+      </c>
+      <c r="C107" t="s">
+        <v>216</v>
+      </c>
+      <c r="D107" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" t="s">
+        <v>218</v>
+      </c>
+      <c r="D108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" t="s">
+        <v>220</v>
+      </c>
+      <c r="D109" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>221</v>
+      </c>
+      <c r="C110" t="s">
+        <v>222</v>
+      </c>
+      <c r="D110" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>223</v>
+      </c>
+      <c r="C111" t="s">
+        <v>224</v>
+      </c>
+      <c r="D111" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>225</v>
+      </c>
+      <c r="C112" t="s">
+        <v>226</v>
+      </c>
+      <c r="D112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>227</v>
+      </c>
+      <c r="C113" t="s">
+        <v>228</v>
+      </c>
+      <c r="D113" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>229</v>
+      </c>
+      <c r="C114" t="s">
+        <v>230</v>
+      </c>
+      <c r="D114" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" t="s">
+        <v>232</v>
+      </c>
+      <c r="D115" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>233</v>
+      </c>
+      <c r="C116" t="s">
+        <v>234</v>
+      </c>
+      <c r="D116" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>235</v>
+      </c>
+      <c r="C117" t="s">
+        <v>236</v>
+      </c>
+      <c r="D117" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>237</v>
+      </c>
+      <c r="C118" t="s">
+        <v>238</v>
+      </c>
+      <c r="D118" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>239</v>
+      </c>
+      <c r="C119" t="s">
+        <v>240</v>
+      </c>
+      <c r="D119" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>241</v>
+      </c>
+      <c r="C120" t="s">
+        <v>242</v>
+      </c>
+      <c r="D120" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>243</v>
+      </c>
+      <c r="C121" t="s">
+        <v>244</v>
+      </c>
+      <c r="D121" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>245</v>
+      </c>
+      <c r="C122" t="s">
+        <v>246</v>
+      </c>
+      <c r="D122" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>247</v>
+      </c>
+      <c r="C123" t="s">
+        <v>248</v>
+      </c>
+      <c r="D123" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>249</v>
+      </c>
+      <c r="C124" t="s">
+        <v>250</v>
+      </c>
+      <c r="D124" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>251</v>
+      </c>
+      <c r="C125" t="s">
+        <v>252</v>
+      </c>
+      <c r="D125" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>253</v>
+      </c>
+      <c r="C126" t="s">
+        <v>254</v>
+      </c>
+      <c r="D126" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>255</v>
+      </c>
+      <c r="C127" t="s">
+        <v>256</v>
+      </c>
+      <c r="D127" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>257</v>
+      </c>
+      <c r="C128" t="s">
+        <v>258</v>
+      </c>
+      <c r="D128" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>259</v>
+      </c>
+      <c r="C129" t="s">
+        <v>260</v>
+      </c>
+      <c r="D129" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>261</v>
+      </c>
+      <c r="C130" t="s">
+        <v>262</v>
+      </c>
+      <c r="D130" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>263</v>
+      </c>
+      <c r="C131" t="s">
+        <v>264</v>
+      </c>
+      <c r="D131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>265</v>
+      </c>
+      <c r="C132" t="s">
+        <v>266</v>
+      </c>
+      <c r="D132" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>267</v>
+      </c>
+      <c r="C133" t="s">
+        <v>268</v>
+      </c>
+      <c r="D133" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>269</v>
+      </c>
+      <c r="C134" t="s">
+        <v>270</v>
+      </c>
+      <c r="D134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>271</v>
+      </c>
+      <c r="C135" t="s">
+        <v>272</v>
+      </c>
+      <c r="D135" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>273</v>
+      </c>
+      <c r="C136" t="s">
+        <v>274</v>
+      </c>
+      <c r="D136" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>275</v>
+      </c>
+      <c r="C137" t="s">
+        <v>276</v>
+      </c>
+      <c r="D137" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>277</v>
+      </c>
+      <c r="C138" t="s">
+        <v>278</v>
+      </c>
+      <c r="D138" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>279</v>
+      </c>
+      <c r="C139" t="s">
+        <v>280</v>
+      </c>
+      <c r="D139" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>281</v>
+      </c>
+      <c r="C140" t="s">
+        <v>282</v>
+      </c>
+      <c r="D140" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>283</v>
+      </c>
+      <c r="C141" t="s">
+        <v>284</v>
+      </c>
+      <c r="D141" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>285</v>
+      </c>
+      <c r="C142" t="s">
+        <v>286</v>
+      </c>
+      <c r="D142" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>287</v>
+      </c>
+      <c r="C143" t="s">
+        <v>288</v>
+      </c>
+      <c r="D143" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>289</v>
+      </c>
+      <c r="C144" t="s">
+        <v>290</v>
+      </c>
+      <c r="D144" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>291</v>
+      </c>
+      <c r="C145" t="s">
+        <v>292</v>
+      </c>
+      <c r="D145" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>293</v>
+      </c>
+      <c r="C146" t="s">
+        <v>294</v>
+      </c>
+      <c r="D146" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>295</v>
+      </c>
+      <c r="C147" t="s">
+        <v>296</v>
+      </c>
+      <c r="D147" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>297</v>
+      </c>
+      <c r="C148" t="s">
+        <v>298</v>
+      </c>
+      <c r="D148" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>299</v>
+      </c>
+      <c r="C149" t="s">
+        <v>300</v>
+      </c>
+      <c r="D149" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>301</v>
+      </c>
+      <c r="C150" t="s">
+        <v>302</v>
+      </c>
+      <c r="D150" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>303</v>
+      </c>
+      <c r="C151" t="s">
+        <v>304</v>
+      </c>
+      <c r="D151" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>305</v>
+      </c>
+      <c r="C152" t="s">
+        <v>306</v>
+      </c>
+      <c r="D152" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>307</v>
+      </c>
+      <c r="C153" t="s">
+        <v>308</v>
+      </c>
+      <c r="D153" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>309</v>
+      </c>
+      <c r="C154" t="s">
+        <v>310</v>
+      </c>
+      <c r="D154" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>311</v>
+      </c>
+      <c r="C155" t="s">
+        <v>312</v>
+      </c>
+      <c r="D155" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>313</v>
+      </c>
+      <c r="C156" t="s">
+        <v>314</v>
+      </c>
+      <c r="D156" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>315</v>
+      </c>
+      <c r="C157" t="s">
+        <v>316</v>
+      </c>
+      <c r="D157" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>317</v>
+      </c>
+      <c r="C158" t="s">
+        <v>318</v>
+      </c>
+      <c r="D158" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>319</v>
+      </c>
+      <c r="C159" t="s">
+        <v>320</v>
+      </c>
+      <c r="D159" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>321</v>
+      </c>
+      <c r="C160" t="s">
+        <v>322</v>
+      </c>
+      <c r="D160" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>323</v>
+      </c>
+      <c r="C161" t="s">
+        <v>324</v>
+      </c>
+      <c r="D161" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>325</v>
+      </c>
+      <c r="C162" t="s">
+        <v>326</v>
+      </c>
+      <c r="D162" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>327</v>
+      </c>
+      <c r="C163" t="s">
+        <v>328</v>
+      </c>
+      <c r="D163" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>329</v>
+      </c>
+      <c r="C164" t="s">
+        <v>330</v>
+      </c>
+      <c r="D164" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>331</v>
+      </c>
+      <c r="C165" t="s">
+        <v>332</v>
+      </c>
+      <c r="D165" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>333</v>
+      </c>
+      <c r="C166" t="s">
+        <v>334</v>
+      </c>
+      <c r="D166" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>335</v>
+      </c>
+      <c r="C167" t="s">
+        <v>336</v>
+      </c>
+      <c r="D167" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>337</v>
+      </c>
+      <c r="C168" t="s">
+        <v>338</v>
+      </c>
+      <c r="D168" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>339</v>
+      </c>
+      <c r="C169" t="s">
+        <v>340</v>
+      </c>
+      <c r="D169" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>341</v>
+      </c>
+      <c r="C170" t="s">
+        <v>342</v>
+      </c>
+      <c r="D170" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>343</v>
+      </c>
+      <c r="C171" t="s">
+        <v>344</v>
+      </c>
+      <c r="D171" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>345</v>
+      </c>
+      <c r="C172" t="s">
+        <v>346</v>
+      </c>
+      <c r="D172" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
+        <v>347</v>
+      </c>
+      <c r="C173" t="s">
+        <v>348</v>
+      </c>
+      <c r="D173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B174" t="s">
+        <v>349</v>
+      </c>
+      <c r="C174" t="s">
+        <v>350</v>
+      </c>
+      <c r="D174" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
+        <v>351</v>
+      </c>
+      <c r="C175" t="s">
+        <v>352</v>
+      </c>
+      <c r="D175" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>353</v>
+      </c>
+      <c r="C176" t="s">
+        <v>354</v>
+      </c>
+      <c r="D176" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
+        <v>355</v>
+      </c>
+      <c r="C177" t="s">
+        <v>356</v>
+      </c>
+      <c r="D177" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>357</v>
+      </c>
+      <c r="C178" t="s">
+        <v>358</v>
+      </c>
+      <c r="D178" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B179" t="s">
+        <v>359</v>
+      </c>
+      <c r="C179" t="s">
+        <v>360</v>
+      </c>
+      <c r="D179" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>361</v>
+      </c>
+      <c r="C180" t="s">
+        <v>362</v>
+      </c>
+      <c r="D180" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
+        <v>363</v>
+      </c>
+      <c r="C181" t="s">
+        <v>364</v>
+      </c>
+      <c r="D181" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B182" t="s">
+        <v>365</v>
+      </c>
+      <c r="C182" t="s">
+        <v>366</v>
+      </c>
+      <c r="D182" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B183" t="s">
+        <v>367</v>
+      </c>
+      <c r="C183" t="s">
+        <v>368</v>
+      </c>
+      <c r="D183" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B184" t="s">
+        <v>369</v>
+      </c>
+      <c r="C184" t="s">
+        <v>370</v>
+      </c>
+      <c r="D184" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B185" t="s">
+        <v>371</v>
+      </c>
+      <c r="C185" t="s">
+        <v>372</v>
+      </c>
+      <c r="D185" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B186" t="s">
+        <v>373</v>
+      </c>
+      <c r="C186" t="s">
+        <v>374</v>
+      </c>
+      <c r="D186" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B187" t="s">
+        <v>375</v>
+      </c>
+      <c r="C187" t="s">
+        <v>376</v>
+      </c>
+      <c r="D187" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
+        <v>377</v>
+      </c>
+      <c r="C188" t="s">
+        <v>378</v>
+      </c>
+      <c r="D188" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B189" t="s">
+        <v>379</v>
+      </c>
+      <c r="C189" t="s">
+        <v>380</v>
+      </c>
+      <c r="D189" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B190" t="s">
+        <v>381</v>
+      </c>
+      <c r="C190" t="s">
+        <v>382</v>
+      </c>
+      <c r="D190" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B191" t="s">
+        <v>383</v>
+      </c>
+      <c r="C191" t="s">
+        <v>384</v>
+      </c>
+      <c r="D191" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B192" t="s">
+        <v>385</v>
+      </c>
+      <c r="C192" t="s">
+        <v>386</v>
+      </c>
+      <c r="D192" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B193" t="s">
+        <v>387</v>
+      </c>
+      <c r="C193" t="s">
+        <v>388</v>
+      </c>
+      <c r="D193" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B194" t="s">
+        <v>389</v>
+      </c>
+      <c r="C194" t="s">
+        <v>390</v>
+      </c>
+      <c r="D194" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B195" t="s">
+        <v>391</v>
+      </c>
+      <c r="C195" t="s">
+        <v>392</v>
+      </c>
+      <c r="D195" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B196" t="s">
+        <v>393</v>
+      </c>
+      <c r="C196" t="s">
+        <v>394</v>
+      </c>
+      <c r="D196" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B197" t="s">
+        <v>395</v>
+      </c>
+      <c r="C197" t="s">
+        <v>396</v>
+      </c>
+      <c r="D197" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B198" t="s">
+        <v>397</v>
+      </c>
+      <c r="C198" t="s">
+        <v>398</v>
+      </c>
+      <c r="D198" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B199" t="s">
+        <v>399</v>
+      </c>
+      <c r="C199" t="s">
+        <v>400</v>
+      </c>
+      <c r="D199" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B200" t="s">
+        <v>401</v>
+      </c>
+      <c r="C200" t="s">
+        <v>402</v>
+      </c>
+      <c r="D200" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
+        <v>403</v>
+      </c>
+      <c r="C201" t="s">
+        <v>404</v>
+      </c>
+      <c r="D201" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B202" t="s">
+        <v>405</v>
+      </c>
+      <c r="C202" t="s">
+        <v>406</v>
+      </c>
+      <c r="D202" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B203" t="s">
+        <v>407</v>
+      </c>
+      <c r="C203" t="s">
+        <v>408</v>
+      </c>
+      <c r="D203" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B204" t="s">
+        <v>409</v>
+      </c>
+      <c r="C204" t="s">
+        <v>410</v>
+      </c>
+      <c r="D204" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B205" t="s">
+        <v>411</v>
+      </c>
+      <c r="C205" t="s">
+        <v>412</v>
+      </c>
+      <c r="D205" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B206" t="s">
+        <v>413</v>
+      </c>
+      <c r="C206" t="s">
+        <v>414</v>
+      </c>
+      <c r="D206" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B207" t="s">
+        <v>415</v>
+      </c>
+      <c r="C207" t="s">
+        <v>416</v>
+      </c>
+      <c r="D207" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B208" t="s">
+        <v>417</v>
+      </c>
+      <c r="C208" t="s">
+        <v>418</v>
+      </c>
+      <c r="D208" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B209" t="s">
+        <v>419</v>
+      </c>
+      <c r="C209" t="s">
+        <v>420</v>
+      </c>
+      <c r="D209" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B210" t="s">
+        <v>421</v>
+      </c>
+      <c r="C210" t="s">
+        <v>422</v>
+      </c>
+      <c r="D210" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B211" t="s">
+        <v>423</v>
+      </c>
+      <c r="C211" t="s">
+        <v>424</v>
+      </c>
+      <c r="D211" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B212" t="s">
+        <v>425</v>
+      </c>
+      <c r="C212" t="s">
+        <v>426</v>
+      </c>
+      <c r="D212" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B213" t="s">
+        <v>427</v>
+      </c>
+      <c r="C213" t="s">
+        <v>428</v>
+      </c>
+      <c r="D213" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B214" t="s">
+        <v>429</v>
+      </c>
+      <c r="C214" t="s">
+        <v>430</v>
+      </c>
+      <c r="D214" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B215" t="s">
+        <v>431</v>
+      </c>
+      <c r="C215" t="s">
+        <v>432</v>
+      </c>
+      <c r="D215" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B216" t="s">
+        <v>433</v>
+      </c>
+      <c r="C216" t="s">
+        <v>434</v>
+      </c>
+      <c r="D216" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B217" t="s">
+        <v>435</v>
+      </c>
+      <c r="C217" t="s">
+        <v>436</v>
+      </c>
+      <c r="D217" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B218" t="s">
+        <v>437</v>
+      </c>
+      <c r="C218" t="s">
+        <v>438</v>
+      </c>
+      <c r="D218" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B219" t="s">
+        <v>439</v>
+      </c>
+      <c r="C219" t="s">
+        <v>440</v>
+      </c>
+      <c r="D219" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B220" t="s">
+        <v>441</v>
+      </c>
+      <c r="C220" t="s">
+        <v>442</v>
+      </c>
+      <c r="D220" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B221" t="s">
+        <v>443</v>
+      </c>
+      <c r="C221" t="s">
+        <v>444</v>
+      </c>
+      <c r="D221" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B222" t="s">
+        <v>445</v>
+      </c>
+      <c r="C222" t="s">
+        <v>446</v>
+      </c>
+      <c r="D222" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B223" t="s">
+        <v>447</v>
+      </c>
+      <c r="C223" t="s">
+        <v>448</v>
+      </c>
+      <c r="D223" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B224" t="s">
+        <v>449</v>
+      </c>
+      <c r="C224" t="s">
+        <v>450</v>
+      </c>
+      <c r="D224" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B225" t="s">
+        <v>451</v>
+      </c>
+      <c r="C225" t="s">
+        <v>452</v>
+      </c>
+      <c r="D225" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B226" t="s">
+        <v>453</v>
+      </c>
+      <c r="C226" t="s">
+        <v>454</v>
+      </c>
+      <c r="D226" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B227" t="s">
+        <v>455</v>
+      </c>
+      <c r="C227" t="s">
+        <v>456</v>
+      </c>
+      <c r="D227" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B228" t="s">
+        <v>457</v>
+      </c>
+      <c r="C228" t="s">
+        <v>458</v>
+      </c>
+      <c r="D228" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B229" t="s">
+        <v>459</v>
+      </c>
+      <c r="C229" t="s">
+        <v>460</v>
+      </c>
+      <c r="D229" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B230" t="s">
+        <v>461</v>
+      </c>
+      <c r="C230" t="s">
+        <v>462</v>
+      </c>
+      <c r="D230" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B231" t="s">
+        <v>463</v>
+      </c>
+      <c r="C231" t="s">
+        <v>464</v>
+      </c>
+      <c r="D231" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B232" t="s">
+        <v>465</v>
+      </c>
+      <c r="C232" t="s">
+        <v>466</v>
+      </c>
+      <c r="D232" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B233" t="s">
+        <v>467</v>
+      </c>
+      <c r="C233" t="s">
+        <v>468</v>
+      </c>
+      <c r="D233" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B234" t="s">
+        <v>469</v>
+      </c>
+      <c r="C234" t="s">
+        <v>470</v>
+      </c>
+      <c r="D234" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B235" t="s">
+        <v>471</v>
+      </c>
+      <c r="C235" t="s">
+        <v>472</v>
+      </c>
+      <c r="D235" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B236" t="s">
+        <v>473</v>
+      </c>
+      <c r="C236" t="s">
+        <v>474</v>
+      </c>
+      <c r="D236" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B237" t="s">
+        <v>475</v>
+      </c>
+      <c r="C237" t="s">
+        <v>476</v>
+      </c>
+      <c r="D237" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B238" t="s">
+        <v>477</v>
+      </c>
+      <c r="C238" t="s">
+        <v>478</v>
+      </c>
+      <c r="D238" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B239" t="s">
+        <v>479</v>
+      </c>
+      <c r="C239" t="s">
+        <v>480</v>
+      </c>
+      <c r="D239" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B240" t="s">
+        <v>481</v>
+      </c>
+      <c r="C240" t="s">
+        <v>482</v>
+      </c>
+      <c r="D240" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B241" t="s">
+        <v>483</v>
+      </c>
+      <c r="C241" t="s">
+        <v>484</v>
+      </c>
+      <c r="D241" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B242" t="s">
+        <v>485</v>
+      </c>
+      <c r="C242" t="s">
+        <v>486</v>
+      </c>
+      <c r="D242" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B243" t="s">
+        <v>487</v>
+      </c>
+      <c r="C243" t="s">
+        <v>488</v>
+      </c>
+      <c r="D243" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B244" t="s">
+        <v>489</v>
+      </c>
+      <c r="C244" t="s">
+        <v>490</v>
+      </c>
+      <c r="D244" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B245" t="s">
+        <v>491</v>
+      </c>
+      <c r="C245" t="s">
+        <v>492</v>
+      </c>
+      <c r="D245" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B246" t="s">
+        <v>493</v>
+      </c>
+      <c r="C246" t="s">
+        <v>494</v>
+      </c>
+      <c r="D246" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B247" t="s">
+        <v>495</v>
+      </c>
+      <c r="C247" t="s">
+        <v>496</v>
+      </c>
+      <c r="D247" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B248" t="s">
+        <v>497</v>
+      </c>
+      <c r="C248" t="s">
+        <v>498</v>
+      </c>
+      <c r="D248" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B249" t="s">
+        <v>499</v>
+      </c>
+      <c r="C249" t="s">
+        <v>500</v>
+      </c>
+      <c r="D249" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B250" t="s">
+        <v>501</v>
+      </c>
+      <c r="C250" t="s">
+        <v>502</v>
+      </c>
+      <c r="D250" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B251" t="s">
+        <v>503</v>
+      </c>
+      <c r="C251" t="s">
+        <v>504</v>
+      </c>
+      <c r="D251" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B252" t="s">
+        <v>505</v>
+      </c>
+      <c r="C252" t="s">
+        <v>506</v>
+      </c>
+      <c r="D252" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="253" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B253" t="s">
+        <v>507</v>
+      </c>
+      <c r="C253" t="s">
+        <v>508</v>
+      </c>
+      <c r="D253" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B254" t="s">
+        <v>509</v>
+      </c>
+      <c r="C254" t="s">
+        <v>510</v>
+      </c>
+      <c r="D254" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B255" t="s">
+        <v>511</v>
+      </c>
+      <c r="C255" t="s">
+        <v>512</v>
+      </c>
+      <c r="D255" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B256" t="s">
+        <v>513</v>
+      </c>
+      <c r="C256" t="s">
+        <v>514</v>
+      </c>
+      <c r="D256" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="257" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B257" t="s">
+        <v>515</v>
+      </c>
+      <c r="C257" t="s">
+        <v>516</v>
+      </c>
+      <c r="D257" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="258" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B258" t="s">
+        <v>517</v>
+      </c>
+      <c r="C258" t="s">
+        <v>518</v>
+      </c>
+      <c r="D258" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B259" t="s">
+        <v>519</v>
+      </c>
+      <c r="C259" t="s">
+        <v>520</v>
+      </c>
+      <c r="D259" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B260" t="s">
+        <v>521</v>
+      </c>
+      <c r="C260" t="s">
+        <v>522</v>
+      </c>
+      <c r="D260" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B261" t="s">
+        <v>523</v>
+      </c>
+      <c r="C261" t="s">
+        <v>524</v>
+      </c>
+      <c r="D261" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="262" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B262" t="s">
+        <v>525</v>
+      </c>
+      <c r="C262" t="s">
+        <v>526</v>
+      </c>
+      <c r="D262" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B263" t="s">
+        <v>527</v>
+      </c>
+      <c r="C263" t="s">
+        <v>528</v>
+      </c>
+      <c r="D263" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B264" t="s">
+        <v>529</v>
+      </c>
+      <c r="C264" t="s">
+        <v>530</v>
+      </c>
+      <c r="D264" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="265" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B265" t="s">
+        <v>531</v>
+      </c>
+      <c r="C265" t="s">
+        <v>532</v>
+      </c>
+      <c r="D265" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="266" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B266" t="s">
+        <v>533</v>
+      </c>
+      <c r="C266" t="s">
+        <v>534</v>
+      </c>
+      <c r="D266" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="267" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B267" t="s">
+        <v>535</v>
+      </c>
+      <c r="C267" t="s">
+        <v>536</v>
+      </c>
+      <c r="D267" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B268" t="s">
+        <v>537</v>
+      </c>
+      <c r="C268" t="s">
+        <v>538</v>
+      </c>
+      <c r="D268" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B269" t="s">
+        <v>539</v>
+      </c>
+      <c r="C269" t="s">
+        <v>540</v>
+      </c>
+      <c r="D269" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="270" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B270" t="s">
+        <v>541</v>
+      </c>
+      <c r="C270" t="s">
+        <v>542</v>
+      </c>
+      <c r="D270" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B271" t="s">
+        <v>543</v>
+      </c>
+      <c r="C271" t="s">
+        <v>544</v>
+      </c>
+      <c r="D271" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B272" t="s">
+        <v>545</v>
+      </c>
+      <c r="C272" t="s">
+        <v>546</v>
+      </c>
+      <c r="D272" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B273" t="s">
+        <v>547</v>
+      </c>
+      <c r="C273" t="s">
+        <v>548</v>
+      </c>
+      <c r="D273" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B274" t="s">
+        <v>549</v>
+      </c>
+      <c r="C274" t="s">
+        <v>550</v>
+      </c>
+      <c r="D274" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B275" t="s">
+        <v>551</v>
+      </c>
+      <c r="C275" t="s">
+        <v>552</v>
+      </c>
+      <c r="D275" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B276" t="s">
+        <v>553</v>
+      </c>
+      <c r="C276" t="s">
+        <v>554</v>
+      </c>
+      <c r="D276" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="277" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B277" t="s">
+        <v>555</v>
+      </c>
+      <c r="C277" t="s">
+        <v>556</v>
+      </c>
+      <c r="D277" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B278" t="s">
+        <v>557</v>
+      </c>
+      <c r="C278" t="s">
+        <v>558</v>
+      </c>
+      <c r="D278" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B279" t="s">
+        <v>559</v>
+      </c>
+      <c r="C279" t="s">
+        <v>560</v>
+      </c>
+      <c r="D279" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="280" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B280" t="s">
+        <v>561</v>
+      </c>
+      <c r="C280" t="s">
+        <v>562</v>
+      </c>
+      <c r="D280" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="281" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B281" t="s">
+        <v>563</v>
+      </c>
+      <c r="C281" t="s">
+        <v>564</v>
+      </c>
+      <c r="D281" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="282" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B282" t="s">
+        <v>565</v>
+      </c>
+      <c r="C282" t="s">
+        <v>566</v>
+      </c>
+      <c r="D282" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B283" t="s">
+        <v>567</v>
+      </c>
+      <c r="C283" t="s">
+        <v>568</v>
+      </c>
+      <c r="D283" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B284" t="s">
+        <v>569</v>
+      </c>
+      <c r="C284" t="s">
+        <v>570</v>
+      </c>
+      <c r="D284" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B285" t="s">
+        <v>571</v>
+      </c>
+      <c r="C285" t="s">
+        <v>572</v>
+      </c>
+      <c r="D285" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="286" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B286" t="s">
+        <v>573</v>
+      </c>
+      <c r="C286" t="s">
+        <v>574</v>
+      </c>
+      <c r="D286" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B287" t="s">
+        <v>575</v>
+      </c>
+      <c r="C287" t="s">
+        <v>576</v>
+      </c>
+      <c r="D287" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B288" t="s">
+        <v>577</v>
+      </c>
+      <c r="C288" t="s">
+        <v>578</v>
+      </c>
+      <c r="D288" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="289" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B289" t="s">
+        <v>579</v>
+      </c>
+      <c r="C289" t="s">
+        <v>580</v>
+      </c>
+      <c r="D289" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B290" t="s">
+        <v>581</v>
+      </c>
+      <c r="C290" t="s">
+        <v>582</v>
+      </c>
+      <c r="D290" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="291" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B291" t="s">
+        <v>583</v>
+      </c>
+      <c r="C291" t="s">
+        <v>584</v>
+      </c>
+      <c r="D291" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="292" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B292" t="s">
+        <v>585</v>
+      </c>
+      <c r="C292" t="s">
+        <v>586</v>
+      </c>
+      <c r="D292" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B293" t="s">
+        <v>587</v>
+      </c>
+      <c r="C293" t="s">
+        <v>588</v>
+      </c>
+      <c r="D293" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B294" t="s">
+        <v>589</v>
+      </c>
+      <c r="C294" t="s">
+        <v>590</v>
+      </c>
+      <c r="D294" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B295" t="s">
+        <v>591</v>
+      </c>
+      <c r="C295" t="s">
+        <v>592</v>
+      </c>
+      <c r="D295" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="296" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B296" t="s">
+        <v>593</v>
+      </c>
+      <c r="C296" t="s">
+        <v>594</v>
+      </c>
+      <c r="D296" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="297" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B297" t="s">
+        <v>595</v>
+      </c>
+      <c r="C297" t="s">
+        <v>596</v>
+      </c>
+      <c r="D297" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="298" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B298" t="s">
+        <v>597</v>
+      </c>
+      <c r="C298" t="s">
+        <v>598</v>
+      </c>
+      <c r="D298" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="299" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B299" t="s">
+        <v>599</v>
+      </c>
+      <c r="C299" t="s">
+        <v>600</v>
+      </c>
+      <c r="D299" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="300" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B300" t="s">
+        <v>601</v>
+      </c>
+      <c r="C300" t="s">
+        <v>602</v>
+      </c>
+      <c r="D300" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B301" t="s">
+        <v>603</v>
+      </c>
+      <c r="C301" t="s">
+        <v>604</v>
+      </c>
+      <c r="D301" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B302" t="s">
+        <v>605</v>
+      </c>
+      <c r="C302" t="s">
+        <v>606</v>
+      </c>
+      <c r="D302" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="303" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B303" t="s">
+        <v>607</v>
+      </c>
+      <c r="C303" t="s">
+        <v>608</v>
+      </c>
+      <c r="D303" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="304" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B304" t="s">
+        <v>609</v>
+      </c>
+      <c r="C304" t="s">
+        <v>610</v>
+      </c>
+      <c r="D304" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="305" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B305" t="s">
+        <v>611</v>
+      </c>
+      <c r="C305" t="s">
+        <v>612</v>
+      </c>
+      <c r="D305" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B306" t="s">
+        <v>613</v>
+      </c>
+      <c r="C306" t="s">
+        <v>614</v>
+      </c>
+      <c r="D306" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="307" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B307" t="s">
+        <v>615</v>
+      </c>
+      <c r="C307" t="s">
+        <v>616</v>
+      </c>
+      <c r="D307" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B308" t="s">
+        <v>617</v>
+      </c>
+      <c r="C308" t="s">
+        <v>618</v>
+      </c>
+      <c r="D308" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="309" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B309" t="s">
+        <v>619</v>
+      </c>
+      <c r="C309" t="s">
+        <v>620</v>
+      </c>
+      <c r="D309" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B310" t="s">
+        <v>621</v>
+      </c>
+      <c r="C310" t="s">
+        <v>622</v>
+      </c>
+      <c r="D310" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B311" t="s">
+        <v>623</v>
+      </c>
+      <c r="C311" t="s">
+        <v>624</v>
+      </c>
+      <c r="D311" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B312" t="s">
+        <v>625</v>
+      </c>
+      <c r="C312" t="s">
+        <v>626</v>
+      </c>
+      <c r="D312" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="313" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B313" t="s">
+        <v>627</v>
+      </c>
+      <c r="C313" t="s">
+        <v>628</v>
+      </c>
+      <c r="D313" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="314" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B314" t="s">
+        <v>629</v>
+      </c>
+      <c r="C314" t="s">
+        <v>630</v>
+      </c>
+      <c r="D314" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="315" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B315" t="s">
+        <v>631</v>
+      </c>
+      <c r="C315" t="s">
+        <v>630</v>
+      </c>
+      <c r="D315" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="316" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B316" t="s">
+        <v>632</v>
+      </c>
+      <c r="C316" t="s">
+        <v>633</v>
+      </c>
+      <c r="D316" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="317" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B317" t="s">
+        <v>634</v>
+      </c>
+      <c r="C317" t="s">
+        <v>635</v>
+      </c>
+      <c r="D317" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="318" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B318" t="s">
+        <v>636</v>
+      </c>
+      <c r="C318" t="s">
+        <v>637</v>
+      </c>
+      <c r="D318" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="319" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B319" t="s">
+        <v>638</v>
+      </c>
+      <c r="C319" t="s">
+        <v>639</v>
+      </c>
+      <c r="D319" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="320" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B320" t="s">
+        <v>640</v>
+      </c>
+      <c r="C320" t="s">
+        <v>641</v>
+      </c>
+      <c r="D320" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="321" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B321" t="s">
+        <v>642</v>
+      </c>
+      <c r="C321" t="s">
+        <v>643</v>
+      </c>
+      <c r="D321" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="322" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B322" t="s">
+        <v>644</v>
+      </c>
+      <c r="C322" t="s">
+        <v>645</v>
+      </c>
+      <c r="D322" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="323" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B323" t="s">
+        <v>646</v>
+      </c>
+      <c r="C323" t="s">
+        <v>647</v>
+      </c>
+      <c r="D323" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="324" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B324" t="s">
+        <v>648</v>
+      </c>
+      <c r="C324" t="s">
+        <v>649</v>
+      </c>
+      <c r="D324" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="325" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B325" t="s">
+        <v>650</v>
+      </c>
+      <c r="C325" t="s">
+        <v>651</v>
+      </c>
+      <c r="D325" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="326" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B326" t="s">
+        <v>652</v>
+      </c>
+      <c r="C326" t="s">
+        <v>653</v>
+      </c>
+      <c r="D326" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="327" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B327" t="s">
+        <v>654</v>
+      </c>
+      <c r="C327" t="s">
+        <v>655</v>
+      </c>
+      <c r="D327" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="328" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B328" t="s">
+        <v>656</v>
+      </c>
+      <c r="C328" t="s">
+        <v>657</v>
+      </c>
+      <c r="D328" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="329" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B329" t="s">
+        <v>658</v>
+      </c>
+      <c r="C329" t="s">
+        <v>659</v>
+      </c>
+      <c r="D329" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="330" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B330" t="s">
+        <v>660</v>
+      </c>
+      <c r="C330" t="s">
+        <v>661</v>
+      </c>
+      <c r="D330" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="331" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B331" t="s">
+        <v>662</v>
+      </c>
+      <c r="C331" t="s">
+        <v>663</v>
+      </c>
+      <c r="D331" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="332" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B332" t="s">
+        <v>664</v>
+      </c>
+      <c r="C332" t="s">
+        <v>665</v>
+      </c>
+      <c r="D332" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="333" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B333" t="s">
+        <v>666</v>
+      </c>
+      <c r="C333" t="s">
+        <v>667</v>
+      </c>
+      <c r="D333" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="334" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B334" t="s">
+        <v>668</v>
+      </c>
+      <c r="C334" t="s">
+        <v>669</v>
+      </c>
+      <c r="D334" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="335" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B335" t="s">
+        <v>670</v>
+      </c>
+      <c r="C335" t="s">
+        <v>671</v>
+      </c>
+      <c r="D335" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="336" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B336" t="s">
+        <v>672</v>
+      </c>
+      <c r="C336" t="s">
+        <v>673</v>
+      </c>
+      <c r="D336" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="337" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B337" t="s">
+        <v>674</v>
+      </c>
+      <c r="C337" t="s">
+        <v>675</v>
+      </c>
+      <c r="D337" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="338" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B338" t="s">
+        <v>676</v>
+      </c>
+      <c r="C338" t="s">
+        <v>677</v>
+      </c>
+      <c r="D338" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="339" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B339" t="s">
+        <v>678</v>
+      </c>
+      <c r="C339" t="s">
+        <v>679</v>
+      </c>
+      <c r="D339" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="340" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B340" t="s">
+        <v>680</v>
+      </c>
+      <c r="C340" t="s">
+        <v>681</v>
+      </c>
+      <c r="D340" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="341" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B341" t="s">
+        <v>682</v>
+      </c>
+      <c r="C341" t="s">
+        <v>683</v>
+      </c>
+      <c r="D341" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="342" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B342" t="s">
+        <v>684</v>
+      </c>
+      <c r="C342" t="s">
+        <v>685</v>
+      </c>
+      <c r="D342" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="343" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B343" t="s">
+        <v>686</v>
+      </c>
+      <c r="C343" t="s">
+        <v>687</v>
+      </c>
+      <c r="D343" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="344" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B344" t="s">
+        <v>688</v>
+      </c>
+      <c r="C344" t="s">
+        <v>689</v>
+      </c>
+      <c r="D344" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="345" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B345" t="s">
+        <v>690</v>
+      </c>
+      <c r="C345" t="s">
+        <v>691</v>
+      </c>
+      <c r="D345" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="346" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B346" t="s">
+        <v>692</v>
+      </c>
+      <c r="C346" t="s">
+        <v>693</v>
+      </c>
+      <c r="D346" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="347" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B347" t="s">
+        <v>694</v>
+      </c>
+      <c r="C347" t="s">
+        <v>695</v>
+      </c>
+      <c r="D347" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="348" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B348" t="s">
+        <v>696</v>
+      </c>
+      <c r="C348" t="s">
+        <v>697</v>
+      </c>
+      <c r="D348" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="349" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B349" t="s">
+        <v>698</v>
+      </c>
+      <c r="C349" t="s">
+        <v>699</v>
+      </c>
+      <c r="D349" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="350" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B350" t="s">
+        <v>700</v>
+      </c>
+      <c r="C350" t="s">
+        <v>701</v>
+      </c>
+      <c r="D350" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="351" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B351" t="s">
+        <v>702</v>
+      </c>
+      <c r="C351" t="s">
+        <v>703</v>
+      </c>
+      <c r="D351" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="352" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B352" t="s">
+        <v>704</v>
+      </c>
+      <c r="C352" t="s">
+        <v>705</v>
+      </c>
+      <c r="D352" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="353" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B353" t="s">
+        <v>706</v>
+      </c>
+      <c r="C353" t="s">
+        <v>707</v>
+      </c>
+      <c r="D353" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="354" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B354" t="s">
+        <v>708</v>
+      </c>
+      <c r="C354" t="s">
+        <v>709</v>
+      </c>
+      <c r="D354" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="355" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B355" t="s">
+        <v>710</v>
+      </c>
+      <c r="C355" t="s">
+        <v>711</v>
+      </c>
+      <c r="D355" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="356" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B356" t="s">
+        <v>712</v>
+      </c>
+      <c r="C356" t="s">
+        <v>713</v>
+      </c>
+      <c r="D356" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="357" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B357" t="s">
+        <v>714</v>
+      </c>
+      <c r="C357" t="s">
+        <v>715</v>
+      </c>
+      <c r="D357" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="358" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B358" t="s">
+        <v>716</v>
+      </c>
+      <c r="C358" t="s">
+        <v>717</v>
+      </c>
+      <c r="D358" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="359" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B359" t="s">
+        <v>718</v>
+      </c>
+      <c r="C359" t="s">
+        <v>719</v>
+      </c>
+      <c r="D359" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="360" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B360" t="s">
+        <v>720</v>
+      </c>
+      <c r="C360" t="s">
+        <v>721</v>
+      </c>
+      <c r="D360" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="361" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B361" t="s">
+        <v>722</v>
+      </c>
+      <c r="C361" t="s">
+        <v>723</v>
+      </c>
+      <c r="D361" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="362" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B362" t="s">
+        <v>724</v>
+      </c>
+      <c r="C362" t="s">
+        <v>725</v>
+      </c>
+      <c r="D362" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="363" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B363" t="s">
+        <v>726</v>
+      </c>
+      <c r="C363" t="s">
+        <v>727</v>
+      </c>
+      <c r="D363" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="364" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B364" t="s">
+        <v>728</v>
+      </c>
+      <c r="C364" t="s">
+        <v>729</v>
+      </c>
+      <c r="D364" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="365" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B365" t="s">
+        <v>730</v>
+      </c>
+      <c r="C365" t="s">
+        <v>731</v>
+      </c>
+      <c r="D365" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="366" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B366" t="s">
+        <v>732</v>
+      </c>
+      <c r="C366" t="s">
+        <v>733</v>
+      </c>
+      <c r="D366" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="367" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B367" t="s">
+        <v>734</v>
+      </c>
+      <c r="C367" t="s">
+        <v>735</v>
+      </c>
+      <c r="D367" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="368" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B368" t="s">
+        <v>736</v>
+      </c>
+      <c r="C368" t="s">
+        <v>737</v>
+      </c>
+      <c r="D368" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="369" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B369" t="s">
+        <v>738</v>
+      </c>
+      <c r="C369" t="s">
+        <v>739</v>
+      </c>
+      <c r="D369" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="370" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B370" t="s">
+        <v>740</v>
+      </c>
+      <c r="C370" t="s">
+        <v>741</v>
+      </c>
+      <c r="D370" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="371" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B371" t="s">
+        <v>742</v>
+      </c>
+      <c r="C371" t="s">
+        <v>743</v>
+      </c>
+      <c r="D371" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="372" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B372" t="s">
+        <v>744</v>
+      </c>
+      <c r="C372" t="s">
+        <v>745</v>
+      </c>
+      <c r="D372" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="373" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B373" t="s">
+        <v>746</v>
+      </c>
+      <c r="C373" t="s">
+        <v>747</v>
+      </c>
+      <c r="D373" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="374" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B374" t="s">
+        <v>748</v>
+      </c>
+      <c r="C374" t="s">
+        <v>749</v>
+      </c>
+      <c r="D374" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="375" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B375" t="s">
+        <v>750</v>
+      </c>
+      <c r="C375" t="s">
+        <v>751</v>
+      </c>
+      <c r="D375" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="376" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B376" t="s">
+        <v>752</v>
+      </c>
+      <c r="C376" t="s">
+        <v>753</v>
+      </c>
+      <c r="D376" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="377" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B377" t="s">
+        <v>754</v>
+      </c>
+      <c r="C377" t="s">
+        <v>755</v>
+      </c>
+      <c r="D377" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="378" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B378" t="s">
+        <v>756</v>
+      </c>
+      <c r="C378" t="s">
+        <v>757</v>
+      </c>
+      <c r="D378" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="379" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B379" t="s">
+        <v>758</v>
+      </c>
+      <c r="C379" t="s">
+        <v>759</v>
+      </c>
+      <c r="D379" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="380" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B380" t="s">
+        <v>760</v>
+      </c>
+      <c r="C380" t="s">
+        <v>761</v>
+      </c>
+      <c r="D380" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="381" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B381" t="s">
+        <v>762</v>
+      </c>
+      <c r="C381" t="s">
+        <v>763</v>
+      </c>
+      <c r="D381" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="382" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B382" t="s">
+        <v>764</v>
+      </c>
+      <c r="C382" t="s">
+        <v>765</v>
+      </c>
+      <c r="D382" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="383" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B383" t="s">
+        <v>766</v>
+      </c>
+      <c r="C383" t="s">
+        <v>767</v>
+      </c>
+      <c r="D383" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="384" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B384" t="s">
+        <v>768</v>
+      </c>
+      <c r="C384" t="s">
+        <v>769</v>
+      </c>
+      <c r="D384" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="385" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B385" t="s">
+        <v>770</v>
+      </c>
+      <c r="C385" t="s">
+        <v>771</v>
+      </c>
+      <c r="D385" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="386" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B386" t="s">
+        <v>772</v>
+      </c>
+      <c r="C386" t="s">
+        <v>773</v>
+      </c>
+      <c r="D386" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="387" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B387" t="s">
+        <v>774</v>
+      </c>
+      <c r="C387" t="s">
+        <v>775</v>
+      </c>
+      <c r="D387" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="388" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B388" t="s">
+        <v>776</v>
+      </c>
+      <c r="C388" t="s">
+        <v>777</v>
+      </c>
+      <c r="D388" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="389" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B389" t="s">
+        <v>778</v>
+      </c>
+      <c r="C389" t="s">
+        <v>779</v>
+      </c>
+      <c r="D389" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="390" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B390" t="s">
+        <v>780</v>
+      </c>
+      <c r="C390" t="s">
+        <v>781</v>
+      </c>
+      <c r="D390" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="391" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B391" t="s">
+        <v>782</v>
+      </c>
+      <c r="C391" t="s">
+        <v>783</v>
+      </c>
+      <c r="D391" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="392" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B392" t="s">
+        <v>784</v>
+      </c>
+      <c r="C392" t="s">
+        <v>785</v>
+      </c>
+      <c r="D392" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="393" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B393" t="s">
+        <v>786</v>
+      </c>
+      <c r="C393" t="s">
+        <v>787</v>
+      </c>
+      <c r="D393" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
